--- a/membership_forms/050_sunflower_tech_club--membership_forms.xlsx
+++ b/membership_forms/050_sunflower_tech_club--membership_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -977,12 +977,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>confirm_password</t>
+          <t>confirm_password_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Confirm Password</t>
+          <t>Confirm Password 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>confirm_accept_terms</t>
+          <t>confirm_accept_terms_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Confirm Accept Terms</t>
+          <t>Confirm Accept Terms 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Payment Method</t>
+          <t>Payment Method2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Billing Address</t>
+          <t>Address2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>City2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>State2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1125,7 +1125,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1252,7 +1252,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>confirm_accept_terms_choices</t>
+          <t>confirm_accept_terms_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1269,7 +1269,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>confirm_accept_terms_choices</t>
+          <t>confirm_accept_terms_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
